--- a/docs/review/packs/chapter-3.8.xlsx
+++ b/docs/review/packs/chapter-3.8.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Use stress radiography where the grade decides the treatment.</t>
+          <t>Grade one is a reduced but present step off, grade two is a flush plateau, and grade three is a plateau posterior to the condyle.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Expect an unreliable arthrometer reading posteriorly and prefer radiography.</t>
+          <t>Grade by step off and record the flexion angle and the limb support used.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Treat the grade as the decision variable and the method of obtaining it as the weak point.</t>
+          <t>Use stress radiography where the grade decides the treatment.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2191,12 +2191,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.8.3-P1</t>
+          <t>3.8.2-P4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.8.3</t>
+          <t>3.8.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Treat single bundle reconstruction as reproducing most of the function here.</t>
+          <t>Expect an unreliable arthrometer reading posteriorly and prefer radiography.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2216,22 +2216,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.8.3-P2</t>
+          <t>3.8.2-P5</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.8.3</t>
+          <t>3.8.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Expect a partial rupture to spare one bundle and give angle specific findings.</t>
+          <t>Treat the grade as the decision variable and the method of obtaining it as the weak point.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2241,12 +2241,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.8.3-P3</t>
+          <t>3.8.2-P6</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.8.3</t>
+          <t>3.8.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Treat the size asymmetry as the argument that settles the single against double bundle question differently from the anterior cruciate.</t>
+          <t>Read a large side to side difference as suggesting a combined injury.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.8.3-P4</t>
+          <t>3.8.3-P1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Place the femoral tunnel within the anterolateral footprint in a single bundle reconstruction.</t>
+          <t>Treat single bundle reconstruction as reproducing most of the function here.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.8.3-P5</t>
+          <t>3.8.3-P2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Treat the cadaveric advantage of double bundle as real and the clinical advantage as unproven.</t>
+          <t>Expect a partial rupture to spare one bundle and give angle specific findings.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.8.3-P6</t>
+          <t>3.8.3-P3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Measure the result with stress radiography rather than by hand.</t>
+          <t>Treat the size asymmetry as the argument that settles the single against double bundle question differently from the anterior cruciate.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2341,22 +2341,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.8.4-P1</t>
+          <t>3.8.3-P4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3.8.4</t>
+          <t>3.8.3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Place a single bundle graft in the anterolateral footprint, since that is the dominant restraint.</t>
+          <t>Place the femoral tunnel within the anterolateral footprint in a single bundle reconstruction.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2366,12 +2366,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.8.4-P2</t>
+          <t>3.8.3-P5</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.8.4</t>
+          <t>3.8.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Treat this bundle's footprint as the target and the tensioning angle as the decision that goes with it.</t>
+          <t>Treat the cadaveric advantage of double bundle as real and the clinical advantage as unproven.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2391,12 +2391,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.8.4-P3</t>
+          <t>3.8.3-P6</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.8.4</t>
+          <t>3.8.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Place the tunnel in the anterolateral footprint and confirm it on imaging.</t>
+          <t>Measure the result with stress radiography rather than by hand.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.8.4-P4</t>
+          <t>3.8.4-P1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Measure the result with stress radiography.</t>
+          <t>Place a single bundle graft in the anterolateral footprint, since that is the dominant restraint.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.8.5-P1</t>
+          <t>3.8.4-P2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.8.5</t>
+          <t>3.8.4</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Expect this bundle's marginal contribution to be smaller than its size suggests.</t>
+          <t>Read apportionment figures with the meniscofemoral handling in mind.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2466,12 +2466,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.8.5-P2</t>
+          <t>3.8.4-P3</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.8.5</t>
+          <t>3.8.4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Treat this bundle as the content of the double bundle question and treat that question as settled in the same unsatisfying way as its anterior counterpart: a cadaveric advantage without a demonstrated clinical one.</t>
+          <t>Treat this bundle's footprint as the target and the tensioning angle as the decision that goes with it.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2491,12 +2491,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.8.5-P3</t>
+          <t>3.8.4-P4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.8.5</t>
+          <t>3.8.4</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Consider double bundle in a combined injury where the corner and capsule are deficient.</t>
+          <t>Place the tunnel in the anterolateral footprint and confirm it on imaging.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2516,12 +2516,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.8.5-P4</t>
+          <t>3.8.4-P5</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.8.5</t>
+          <t>3.8.4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Treat it as selected rather than default, on the current evidence.</t>
+          <t>Measure the result with stress radiography.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2541,12 +2541,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.8.6-P1</t>
+          <t>3.8.5-P1</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.8.6</t>
+          <t>3.8.5</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Prefer stress radiography to arthrometry for posterior laxity.</t>
+          <t>Expect this bundle's marginal contribution to be smaller than its size suggests.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2566,12 +2566,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.8.6-P2</t>
+          <t>3.8.5-P2</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.8.6</t>
+          <t>3.8.5</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Use the quadriceps active test when the sag is uncertain.</t>
+          <t>Read the double bundle gain as real, measurable and small in an otherwise intact knee.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2591,12 +2591,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.8.6-P3</t>
+          <t>3.8.5-P3</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.8.6</t>
+          <t>3.8.5</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Treat the starting position as the thing to control, in examination and in surgery.</t>
+          <t>Treat this bundle as the content of the double bundle question and treat that question as settled in the same unsatisfying way as its anterior counterpart: a cadaveric advantage without a demonstrated clinical one.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2616,12 +2616,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.8.6-P4</t>
+          <t>3.8.5-P4</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.8.6</t>
+          <t>3.8.5</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Check the step off after fixation and before closure.</t>
+          <t>Consider double bundle in a combined injury where the corner and capsule are deficient.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.8.6-P5</t>
+          <t>3.8.5-P5</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.8.6</t>
+          <t>3.8.5</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Measure the result with stress radiography rather than by hand.</t>
+          <t>Treat it as selected rather than default, on the current evidence.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2666,12 +2666,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.8.6-P6</t>
+          <t>3.8.5-P6</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.8.6</t>
+          <t>3.8.5</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Expect some residual laxity and attribute it before revising.</t>
+          <t>State that the subgroup with the strongest mechanical case has no trial evidence.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2691,12 +2691,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P1</t>
+          <t>3.8.6-P1</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.8.7</t>
+          <t>3.8.6</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Expect the strategy to work near extension and less in deeper flexion.</t>
+          <t>Prefer stress radiography to arthrometry for posterior laxity.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2716,22 +2716,22 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P2</t>
+          <t>3.8.6-P2</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.8.7</t>
+          <t>3.8.6</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Treat the adaptation as the reason non operative management succeeds here more often than anteriorly, and as the reason the natural history is still unfavourable in the long term.</t>
+          <t>Use the quadriceps active test when the sag is uncertain.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2741,12 +2741,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P3</t>
+          <t>3.8.6-P3</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.8.7</t>
+          <t>3.8.6</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Address alignment in a varus limb with posterolateral laxity.</t>
+          <t>Treat the starting position as the thing to control, in examination and in surgery.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2766,22 +2766,22 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P1</t>
+          <t>3.8.6-P4</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>- The tibia must be pulled out of its sag before fixation.</t>
+          <t>Check the step off after fixation and before closure.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2791,22 +2791,22 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P2</t>
+          <t>3.8.6-P5</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Expect the tibial side to be the weaker end and choose fixation accordingly.</t>
+          <t>Measure the result with stress radiography rather than by hand.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2816,12 +2816,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P3</t>
+          <t>3.8.6-P6</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Treat the reconstruction as a construct in an environment, as anteriorly, and note that the environment here is dominated by the posterolateral corner and by alignment.</t>
+          <t>Expect some residual laxity and attribute it before revising.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,22 +2841,22 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P4</t>
+          <t>3.8.7-P1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Assess and reconstruct the posterolateral corner in the same sitting where it is injured.</t>
+          <t>Grade of laxity and whether the corner is involved.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,22 +2866,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P5</t>
+          <t>3.8.7-P2</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Measure the result with stress radiography rather than by hand.</t>
+          <t>Expect the strategy to work near extension and less in deeper flexion.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,22 +2891,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P6</t>
+          <t>3.8.7-P3</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel trajectories in advance to avoid convergence in a multiligament knee.</t>
+          <t>Treat the adaptation as the reason non operative management succeeds here more often than anteriorly, and as the reason the natural history is still unfavourable in the long term.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,22 +2916,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P7</t>
+          <t>3.8.7-P4</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Consider inlay fixation where a tibial tunnel would converge with another.</t>
+          <t>Grade and corner involvement, which decide whether non operative management is viable.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,22 +2941,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P1</t>
+          <t>3.8.7-P5</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Expect the cadaveric difference to be largest near extension.</t>
+          <t>Address alignment in a varus limb with posterolateral laxity.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,12 +2966,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P2</t>
+          <t>3.8.7-P6</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Treat this as a decision about marginal mechanical gain against definite added complexity, in an operation whose results are already less reliable than its anterior counterpart.</t>
+          <t>State that no measurement predicts which knee will degenerate.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,22 +2991,22 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P3</t>
+          <t>3.8.8-P1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Prefer two bundles where the capsule and corner are deficient and graft allows.</t>
+          <t>- The tibia must be pulled out of its sag before fixation.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,22 +3016,22 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P4</t>
+          <t>3.8.8-P2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Recognise the constraint as a resource one rather than a mechanical one.</t>
+          <t>Expect the tibial side to be the weaker end and choose fixation accordingly.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,22 +3041,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P5</t>
+          <t>3.8.8-P3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel trajectories and bone bridge before committing to two bundles.</t>
+          <t>Treat the reconstruction as a construct in an environment, as anteriorly, and note that the environment here is dominated by the posterolateral corner and by alignment.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,22 +3066,22 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P6</t>
+          <t>3.8.8-P4</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Consider staging where graft and time are both short.</t>
+          <t>Assess and reconstruct the posterolateral corner in the same sitting where it is injured.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,22 +3091,22 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P1</t>
+          <t>3.8.8-P5</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Expect less attenuation mechanically and similar outcomes clinically.</t>
+          <t>Correct varus alignment where it would load the reconstruction.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,12 +3116,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P2</t>
+          <t>3.8.8-P6</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Treat the choice as a construct advantage traded against an operative cost, and note that the trade has shifted as arthroscopic techniques have developed.</t>
+          <t>Measure the result with stress radiography rather than by hand.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,22 +3141,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P3</t>
+          <t>3.8.8-P7</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Consider inlay in revision where a previous tibial tunnel is wide or malpositioned.</t>
+          <t>Plan tunnel trajectories in advance to avoid convergence in a multiligament knee.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,22 +3166,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P4</t>
+          <t>3.8.8-P8</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Consider it in a multiligament knee to avoid tunnel convergence.</t>
+          <t>Consider inlay fixation where a tibial tunnel would converge with another.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,22 +3191,22 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P5</t>
+          <t>3.8.8-P9</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Plan the approach and position from the imaging rather than from habit.</t>
+          <t>State that the optimal sequence for a given combination is not established.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,22 +3216,22 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P6</t>
+          <t>3.8.9-P1</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.9</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Plan the technique from preoperative imaging of the tibia.</t>
+          <t>Expect the cadaveric difference to be largest near extension.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,31 +3241,406 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P7</t>
+          <t>3.8.9-P2</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.9</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Use the inlay where the tibia is compromised and a tunnel is unattractive.</t>
+          <t>Treat this as a decision about marginal mechanical gain against definite added complexity, in an operation whose results are already less reliable than its anterior counterpart.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9-P3</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Decide selectively rather than adopting either technique as a default.</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9-P4</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Prefer two bundles where the capsule and corner are deficient and graft allows.</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9-P5</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Recognise the constraint as a resource one rather than a mechanical one.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9-P6</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Plan tunnel trajectories and bone bridge before committing to two bundles.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9-P7</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Consider staging where graft and time are both short.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9-P8</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.8.9</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Accept that the trade off point is not established.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P1</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Expect less attenuation mechanically and similar outcomes clinically.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P2</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Treat the choice as a construct advantage traded against an operative cost, and note that the trade has shifted as arthroscopic techniques have developed.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P3</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Consider inlay in revision where a previous tibial tunnel is wide or malpositioned.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P4</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Consider it in a multiligament knee to avoid tunnel convergence.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P5</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Plan the approach and position from the imaging rather than from habit.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P6</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Plan the technique from preoperative imaging of the tibia.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P7</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Set up the position and approach for the technique chosen rather than deciding in theatre.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P8</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Use the inlay where the tibia is compromised and a tunnel is unattractive.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P9</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Accept that the choice rests on judgement about the particular tibia.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3927,7 +4302,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>53</f>
+        <f>68</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3942,7 +4317,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3972,7 +4347,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3984,7 +4359,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -3996,7 +4371,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -4008,7 +4383,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E55,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E70,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.8.xlsx
+++ b/docs/review/packs/chapter-3.8.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Prefer stress radiography to arthrometry for posterior laxity.</t>
+          <t>Record the step off and the flexion angle, not a drawer figure alone.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Use the quadriceps active test when the sag is uncertain.</t>
+          <t>Prefer stress radiography to arthrometry for posterior laxity.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Treat the starting position as the thing to control, in examination and in surgery.</t>
+          <t>Use the quadriceps active test when the sag is uncertain.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Check the step off after fixation and before closure.</t>
+          <t>Treat the starting position as the thing to control, in examination and in surgery.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Measure the result with stress radiography rather than by hand.</t>
+          <t>Check the step off after fixation and before closure.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Expect some residual laxity and attribute it before revising.</t>
+          <t>Measure the result with stress radiography rather than by hand.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,22 +2841,22 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P1</t>
+          <t>3.8.6-P7</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.8.7</t>
+          <t>3.8.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Grade of laxity and whether the corner is involved.</t>
+          <t>Expect some residual laxity and attribute it before revising.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P2</t>
+          <t>3.8.7-P1</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Expect the strategy to work near extension and less in deeper flexion.</t>
+          <t>Grade of laxity and whether the corner is involved.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P3</t>
+          <t>3.8.7-P2</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Treat the adaptation as the reason non operative management succeeds here more often than anteriorly, and as the reason the natural history is still unfavourable in the long term.</t>
+          <t>Expect the strategy to work near extension and less in deeper flexion.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P4</t>
+          <t>3.8.7-P3</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Grade and corner involvement, which decide whether non operative management is viable.</t>
+          <t>Ask about descending tasks specifically, since they demand most.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,7 +2941,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P5</t>
+          <t>3.8.7-P4</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Address alignment in a varus limb with posterolateral laxity.</t>
+          <t>Treat the adaptation as the reason non operative management succeeds here more often than anteriorly, and as the reason the natural history is still unfavourable in the long term.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,7 +2966,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.8.7-P6</t>
+          <t>3.8.7-P5</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>State that no measurement predicts which knee will degenerate.</t>
+          <t>Grade and corner involvement, which decide whether non operative management is viable.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,22 +2991,22 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P1</t>
+          <t>3.8.7-P6</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>- The tibia must be pulled out of its sag before fixation.</t>
+          <t>Address alignment in a varus limb with posterolateral laxity.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,22 +3016,22 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P2</t>
+          <t>3.8.7-P7</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Expect the tibial side to be the weaker end and choose fixation accordingly.</t>
+          <t>Counsel that reconstruction improves laxity without a clear effect on the natural history.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,12 +3041,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P3</t>
+          <t>3.8.7-P8</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.8.8</t>
+          <t>3.8.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Treat the reconstruction as a construct in an environment, as anteriorly, and note that the environment here is dominated by the posterolateral corner and by alignment.</t>
+          <t>State that no measurement predicts which knee will degenerate.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,7 +3066,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P4</t>
+          <t>3.8.8-P1</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Assess and reconstruct the posterolateral corner in the same sitting where it is injured.</t>
+          <t>- The tibia must be pulled out of its sag before fixation.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,7 +3091,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P5</t>
+          <t>3.8.8-P2</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Correct varus alignment where it would load the reconstruction.</t>
+          <t>Expect the tibial side to be the weaker end and choose fixation accordingly.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P6</t>
+          <t>3.8.8-P3</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Measure the result with stress radiography rather than by hand.</t>
+          <t>Treat the reconstruction as a construct in an environment, as anteriorly, and note that the environment here is dominated by the posterolateral corner and by alignment.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,7 +3141,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P7</t>
+          <t>3.8.8-P4</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel trajectories in advance to avoid convergence in a multiligament knee.</t>
+          <t>Assess and reconstruct the posterolateral corner in the same sitting where it is injured.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,7 +3166,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P8</t>
+          <t>3.8.8-P5</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Consider inlay fixation where a tibial tunnel would converge with another.</t>
+          <t>Correct varus alignment where it would load the reconstruction.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.8.8-P9</t>
+          <t>3.8.8-P6</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>State that the optimal sequence for a given combination is not established.</t>
+          <t>Measure the result with stress radiography rather than by hand.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,22 +3216,22 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P1</t>
+          <t>3.8.8-P7</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Expect the cadaveric difference to be largest near extension.</t>
+          <t>Plan tunnel trajectories in advance to avoid convergence in a multiligament knee.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,22 +3241,22 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P2</t>
+          <t>3.8.8-P8</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Treat this as a decision about marginal mechanical gain against definite added complexity, in an operation whose results are already less reliable than its anterior counterpart.</t>
+          <t>Consider inlay fixation where a tibial tunnel would converge with another.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3266,22 +3266,22 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P3</t>
+          <t>3.8.8-P9</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>3.8.9</t>
+          <t>3.8.8</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Decide selectively rather than adopting either technique as a default.</t>
+          <t>State that the optimal sequence for a given combination is not established.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P4</t>
+          <t>3.8.9-P1</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Prefer two bundles where the capsule and corner are deficient and graft allows.</t>
+          <t>Expect the cadaveric difference to be largest near extension.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P5</t>
+          <t>3.8.9-P2</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Recognise the constraint as a resource one rather than a mechanical one.</t>
+          <t>Treat this as a decision about marginal mechanical gain against definite added complexity, in an operation whose results are already less reliable than its anterior counterpart.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3341,7 +3341,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P6</t>
+          <t>3.8.9-P3</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel trajectories and bone bridge before committing to two bundles.</t>
+          <t>Decide selectively rather than adopting either technique as a default.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P7</t>
+          <t>3.8.9-P4</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Consider staging where graft and time are both short.</t>
+          <t>Prefer two bundles where the capsule and corner are deficient and graft allows.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.8.9-P8</t>
+          <t>3.8.9-P5</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Accept that the trade off point is not established.</t>
+          <t>Recognise the constraint as a resource one rather than a mechanical one.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3416,22 +3416,22 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P1</t>
+          <t>3.8.9-P6</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.9</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Expect less attenuation mechanically and similar outcomes clinically.</t>
+          <t>Plan tunnel trajectories and bone bridge before committing to two bundles.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3441,22 +3441,22 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P2</t>
+          <t>3.8.9-P7</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.9</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Treat the choice as a construct advantage traded against an operative cost, and note that the trade has shifted as arthroscopic techniques have developed.</t>
+          <t>Consider staging where graft and time are both short.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3466,22 +3466,22 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P3</t>
+          <t>3.8.9-P8</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>3.8.10</t>
+          <t>3.8.9</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Consider inlay in revision where a previous tibial tunnel is wide or malpositioned.</t>
+          <t>Accept that the trade off point is not established.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P4</t>
+          <t>3.8.10-P1</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Consider it in a multiligament knee to avoid tunnel convergence.</t>
+          <t>Expect less attenuation mechanically and similar outcomes clinically.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3516,7 +3516,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P5</t>
+          <t>3.8.10-P2</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Plan the approach and position from the imaging rather than from habit.</t>
+          <t>Treat the choice as a construct advantage traded against an operative cost, and note that the trade has shifted as arthroscopic techniques have developed.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3541,7 +3541,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P6</t>
+          <t>3.8.10-P3</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Plan the technique from preoperative imaging of the tibia.</t>
+          <t>Consider inlay in revision where a previous tibial tunnel is wide or malpositioned.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P7</t>
+          <t>3.8.10-P4</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Set up the position and approach for the technique chosen rather than deciding in theatre.</t>
+          <t>Consider it in a multiligament knee to avoid tunnel convergence.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3591,7 +3591,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P8</t>
+          <t>3.8.10-P5</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Use the inlay where the tibia is compromised and a tunnel is unattractive.</t>
+          <t>Plan the approach and position from the imaging rather than from habit.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.8.10-P9</t>
+          <t>3.8.10-P6</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -3631,16 +3631,91 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Accept that the choice rests on judgement about the particular tibia.</t>
+          <t>Plan the technique from preoperative imaging of the tibia.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P7</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Set up the position and approach for the technique chosen rather than deciding in theatre.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P8</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Use the inlay where the tibia is compromised and a tunnel is unattractive.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10-P9</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>3.8.10</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Accept that the choice rests on judgement about the particular tibia.</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4302,7 +4377,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>68</f>
+        <f>71</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -4317,7 +4392,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -4347,7 +4422,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -4359,7 +4434,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -4371,7 +4446,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -4383,7 +4458,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E70,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E73,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
